--- a/docs/public/downloads/sabikan-checklist.xlsx
+++ b/docs/public/downloads/sabikan-checklist.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="40">
   <si>
     <t>サビ管確認チェックリスト</t>
   </si>
@@ -40,13 +40,19 @@
     <t>備考</t>
   </si>
   <si>
-    <t>サービス管理責任者研修修了証</t>
+    <t>① サービス管理責任者等基礎研修修了証</t>
   </si>
   <si>
     <t>☐</t>
   </si>
   <si>
     <t>修了年月：</t>
+  </si>
+  <si>
+    <t>② 相談支援従事者初任者研修（講義部分）修了証</t>
+  </si>
+  <si>
+    <t>③ サービス管理責任者等実践研修修了証</t>
   </si>
   <si>
     <t>履歴書</t>
@@ -593,7 +599,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -687,7 +693,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,7 +704,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -723,93 +729,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="16" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="B16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>10</v>
@@ -820,31 +826,46 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="B28" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-    </row>
-    <row r="29" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>8</v>
+      <c r="B29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -855,86 +876,115 @@
         <v>10</v>
       </c>
       <c r="C30" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>2</v>
-      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>2</v>
+      <c r="A33" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="B36" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-    </row>
-    <row r="37" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="B37" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="9"/>
-    </row>
-    <row r="38" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
+      <c r="B38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="9"/>
-    </row>
-    <row r="39" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+    </row>
+    <row r="41" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="9"/>
+      <c r="B41" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="9"/>
+    </row>
+    <row r="42" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="9"/>
+    </row>
+    <row r="43" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -946,12 +996,12 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>

--- a/docs/public/downloads/sabikan-checklist.xlsx
+++ b/docs/public/downloads/sabikan-checklist.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="41">
   <si>
     <t>サビ管確認チェックリスト</t>
   </si>
@@ -116,6 +116,9 @@
   </si>
   <si>
     <t>勤務開始日を確定した</t>
+  </si>
+  <si>
+    <t>各指定権者のフォーマットを渡して記入してもらう</t>
   </si>
   <si>
     <t>指定申請用職員情報を上位店に共有した</t>
@@ -599,7 +602,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -952,21 +955,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+    <row r="39" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-    </row>
-    <row r="41" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="B39" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="9"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
@@ -985,6 +990,15 @@
         <v>2</v>
       </c>
       <c r="C43" s="9"/>
+    </row>
+    <row r="44" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -998,10 +1012,10 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A41:C41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
